--- a/Result/profitability/2321.xlsx
+++ b/Result/profitability/2321.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.16875</v>
+        <v>-0.145</v>
       </c>
       <c r="N2" t="n">
-        <v>28.50125</v>
+        <v>28.85875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.27375</v>
+        <v>-0.19</v>
       </c>
       <c r="N3" t="n">
-        <v>24.6575</v>
+        <v>25.22625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2475</v>
+        <v>-0.13625</v>
       </c>
       <c r="N4" t="n">
-        <v>21.53625</v>
+        <v>22.39125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.365</v>
+        <v>-0.3275</v>
       </c>
       <c r="N5" t="n">
-        <v>17.37375</v>
+        <v>18.15625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.44625</v>
+        <v>-0.4075</v>
       </c>
       <c r="N6" t="n">
-        <v>14.10625</v>
+        <v>14.94125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4975</v>
+        <v>-0.385</v>
       </c>
       <c r="N7" t="n">
-        <v>11.19375</v>
+        <v>12.06875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4775</v>
+        <v>-0.4125</v>
       </c>
       <c r="N8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.8925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.78</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5599999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>4.68625</v>
@@ -1645,7 +1645,7 @@
         <v>-0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5912499999999999</v>
+        <v>-0.5912500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>4.032500000000001</v>
@@ -1772,7 +1772,7 @@
         <v>-0.37</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.55875</v>
+        <v>-0.5587500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>3.91</v>
@@ -1899,7 +1899,7 @@
         <v>-0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6075</v>
+        <v>-0.6074999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>3.6125</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>205</v>
+      </c>
+      <c r="D75" t="n">
+        <v>129</v>
+      </c>
+      <c r="E75" t="n">
+        <v>75</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07250000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.01375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.099999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1253822629969417</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.259999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2049770792403405</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
